--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2021_tarapaca.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -712,13 +712,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="11">
@@ -735,13 +735,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="12">
@@ -758,13 +758,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="13">
@@ -775,19 +775,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="14">
@@ -827,13 +827,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="16">
@@ -850,13 +850,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="17">
@@ -876,7 +876,7 @@
         <v>-0.11</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.43</v>
